--- a/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amandine marche au jardin avec maman. Un chien arrive près de la haie. Il fait ouaf ouaf. Maman dit : c'est un chien. C'est le nom de l'animal. Le cri, c'est ouaf. Amandine répète : un chien. Ouaf. Un chat saute sur le muret. Il fait miaou. Maman dit : c'est un chat. Le cri, c'est miaou. Amandine dit : un chat. Miaou. Plus loin, un canard nage dans la bassine. Il fait coin coin. Maman dit : c'est un canard. Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.</t>
+          <t>Amandine marche au jardin avec maman. Un chien arrive près de la haie. Il fait ouaf ouaf. C'est un chien. C'est le nom de l'animal. Le cri, c'est ouaf. Amandine répète : un chien. Ouaf. Un chat saute sur le muret. Il fait miaou. C'est un chat. Le cri, c'est miaou. Un chat. Miaou. Plus loin, un canard nage dans la bassine. Il fait coin coin. C'est un canard. Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine marche au jardin avec maman. Un chien arrive près de la haie. Il fait ouaf ouaf.
+maman|C'est un chien. C'est le nom de l'animal.
+narrateur|Le cri, c'est ouaf. Amandine répète : un chien. Ouaf. Un chat saute sur le muret. Il fait miaou.
+maman|C'est un chat.
+narrateur|Le cri, c'est miaou.
+enfant-f|Un chat. Miaou. Plus loin, un canard nage dans la bassine. Il fait coin coin.
+maman|C'est un canard.
+narrateur|Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine entend un animal. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine a dit le nom de l'animal. Elle a dit le cri. Chien. Chat. Canard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine donne la main à maman. Le jardin sent l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc,chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Amandine entend un animal. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,11 @@
           <t>narrateur|Amandine a dit le nom de l'animal. Elle a dit le cri. Chien. Chat. Canard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1854,7 @@
           <t>narrateur|Amandine donne la main à maman. Le jardin sent l'herbe.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amandine nomme les cris au jardin</t>
+          <t>Le merle du jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut le merle du cerisier. Il siffle. Un chat miaule. Le merle s'envole. Elles restent près du tronc.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amandine marche au jardin avec maman. Un chien arrive près de la haie. Il fait ouaf ouaf. C'est un chien. C'est le nom de l'animal. Le cri, c'est ouaf. Amandine répète : un chien. Ouaf. Un chat saute sur le muret. Il fait miaou. C'est un chat. Le cri, c'est miaou. Un chat. Miaou. Plus loin, un canard nage dans la bassine. Il fait coin coin. C'est un canard. Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.</t>
+          <t>La terre du jardin reste noire et grasse. Un ver rose se plie sous une feuille. Le cerisier penche au fond, encore mouillé. Ça sent l'humus et l'eau de pluie. Tu vois le ver, Chouchou ? Oui. Je veux le merle. Celui du cerisier ? Celui qui siffle. En ce moment, Chouchou avance entre les rames. Une goutte tombe d'une feuille sur son nez. Un sifflet clair part du cerisier. Le merle ! Tu as entendu ? Il siffle. Le merle siffle. Un point noir se pose sur une branche. Le bec est jaune, tout net. Je le vois. Chouchou s'arrête près du tronc. L'écorce est rêche sous sa paume. Le merle siffle encore, plus haut. Tio tio. C'est son cri. Un bruit plus bas arrive de l'allée. Miaou, tout proche. Qui c'est ? On écoute. Un chat gris glisse le long des rames. Le merle s'envole d'un coup. Une plume noire tombe dans l'herbe. Il est parti. Le chat a miaulé. Le sifflet du merle ne revient pas. Chouchou reste collée au tronc. L'écorce marque sa paume. Il a sifflé avant. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine marche au jardin avec maman. Un chien arrive près de la haie. Il fait ouaf ouaf. Maman dit : c'est un chien. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Le cri, c'est ouaf. Amandine répète : un chien. Ouaf. Un chat saute sur le muret. Il fait miaou. Maman dit : c'est un chat. Le cri, c'est miaou. Amandine dit : un chat. Miaou. Plus loin, un canard nage dans la bassine. Il fait coin coin. Maman dit : c'est un canard. Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La terre du jardin reste noire et grasse. Un ver rose se plie sous une feuille. Le cerisier penche au fond, encore mouillé. Ça sent l'humus et l'eau de pluie. Tu vois le ver, Chouchou ? Oui. Je veux le merle. Celui du cerisier ? Celui qui siffle. En ce moment, Chouchou avance entre les rames. Une goutte tombe d'une feuille sur son nez. Un sifflet clair part du cerisier. Le merle ! Tu as entendu ? Il siffle. Le merle siffle. Un point noir se pose sur une branche. Le bec est jaune, tout net. Je le vois. Chouchou s'arrête près du tronc. L'écorce est rêche sous sa paume. Le merle siffle encore, plus haut. Tio tio. C'est son cri. Un bruit plus bas arrive de l'allée. Miaou, tout proche. Qui c'est ? On écoute. Un chat gris glisse le long des rames. Le merle s'envole d'un coup. Une plume noire tombe dans l'herbe. Il est parti. Le chat a miaulé. Le sifflet du merle ne revient pas. Chouchou reste collée au tronc. L'écorce marque sa paume. Il a sifflé avant. Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,44 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Amandine marche au jardin avec maman. Un chien arrive près de la haie. Il fait ouaf ouaf.
-maman|C'est un chien. C'est le nom de l'animal.
-narrateur|Le cri, c'est ouaf. Amandine répète : un chien. Ouaf. Un chat saute sur le muret. Il fait miaou.
-maman|C'est un chat.
-narrateur|Le cri, c'est miaou.
-enfant-f|Un chat. Miaou. Plus loin, un canard nage dans la bassine. Il fait coin coin.
-maman|C'est un canard.
-narrateur|Le cri, c'est coin coin. Amandine rit. Elle dit le nom de l'animal. Elle dit le cri. Chien, chat, canard. Parce qu'elle a écouté, elle peut nommer.</t>
+          <t>narrateur|La terre du jardin reste noire et grasse.
+narrateur|Un ver rose se plie sous une feuille.
+narrateur|Le cerisier penche au fond, encore mouillé.
+narrateur|Ça sent l'humus et l'eau de pluie.
+maman|Tu vois le ver, Chouchou ?
+enfant-f|Oui.
+enfant-f|Je veux le merle.
+maman|Celui du cerisier ?
+enfant-f|Celui qui siffle.
+narrateur|En ce moment, Chouchou avance entre les rames.
+narrateur|Une goutte tombe d'une feuille sur son nez.
+narrateur|Un sifflet clair part du cerisier.
+enfant-f|Le merle !
+maman|Tu as entendu ?
+enfant-f|Il siffle.
+maman|Le merle siffle.
+narrateur|Un point noir se pose sur une branche.
+narrateur|Le bec est jaune, tout net.
+enfant-f|Je le vois.
+narrateur|Chouchou s'arrête près du tronc.
+narrateur|L'écorce est rêche sous sa paume.
+narrateur|Le merle siffle encore, plus haut.
+enfant-f|Tio tio.
+maman|C'est son cri.
+narrateur|Un bruit plus bas arrive de l'allée.
+narrateur|Miaou, tout proche.
+enfant-f|Qui c'est ?
+maman|On écoute.
+narrateur|Un chat gris glisse le long des rames.
+narrateur|Le merle s'envole d'un coup.
+narrateur|Une plume noire tombe dans l'herbe.
+enfant-f|Il est parti.
+maman|Le chat a miaulé.
+narrateur|Le sifflet du merle ne revient pas.
+narrateur|Chouchou reste collée au tronc.
+narrateur|L'écorce marque sa paume.
+enfant-f|Il a sifflé avant.
+maman|Oui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,12 +1393,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amandine entend un animal. Que dit-elle ?</t>
+          <t>Chouchou a entendu le merle. Quel est le cri du merle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amandine entend un animal. Que dit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a entendu le merle. Quel est le cri du merle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1366,12 +1408,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>chien</t>
+          <t>siffle</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>chien | ouaf | chat | miaou | canard | coin coin</t>
+          <t>siffle | il siffle | tio tio | le cri | le merle</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1386,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle dit le nom de l'animal. Elle dit le cri. Que dit Amandine ?</t>
+          <t>Le merle siffle. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1435,7 +1477,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1549,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Amandine entend un animal. Que dit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou a entendu le merle.
+narrateur|Quel est le cri du merle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amandine a dit le nom de l'animal. Elle a dit le cri. Chien. Chat. Canard.</t>
+          <t>Le chat s'assoit sous le cerisier. Il lèche une patte, tout calme. Le merle n'est plus là. Tu l'as entendu siffler. Merci d'avoir écouté, Chouchou. Il sifflait. Oui. Tio tio. Chouchou ramasse la plume noire. Elle est légère, un peu humide. On reste près du tronc ? Oui. Le chat miaule encore, plus doux. Chouchou ne court pas vers lui. Elle garde la plume dans la main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Elle a dit le cri. Chien. Chat. Canard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat s'assoit sous le cerisier. Il lèche une patte, tout calme. Le merle n'est plus là. Tu l'as entendu siffler. Merci d'avoir écouté, Chouchou. Il sifflait. Oui. Tio tio. Chouchou ramasse la plume noire. Elle est légère, un peu humide. On reste près du tronc ? Oui. Le chat miaule encore, plus doux. Chouchou ne court pas vers lui. Elle garde la plume dans la main.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1645,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1721,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amandine a dit le nom de l'animal. Elle a dit le cri. Chien. Chat. Canard.</t>
+          <t>narrateur|Le chat s'assoit sous le cerisier.
+narrateur|Il lèche une patte, tout calme.
+enfant-f|Le merle n'est plus là.
+maman|Tu l'as entendu siffler.
+maman|Merci d'avoir écouté, Chouchou.
+enfant-f|Il sifflait.
+maman|Oui.
+maman|Tio tio.
+narrateur|Chouchou ramasse la plume noire.
+narrateur|Elle est légère, un peu humide.
+maman|On reste près du tronc ?
+enfant-f|Oui.
+narrateur|Le chat miaule encore, plus doux.
+narrateur|Chouchou ne court pas vers lui.
+narrateur|Elle garde la plume dans la main.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1711,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amandine donne la main à maman. Le jardin sent l'herbe.</t>
+          <t>Le cerisier redevient silencieux. Le ver s'est caché sous la feuille. Le merle va revenir ? Peut-être. Tu as eu son cri. Une goutte tombe encore du bois. Elle fait un trou dans la terre noire. Tio tio. C'était le merle. Le chat part vers l'allée. Chouchou reste près du tronc mouillé. Tu voulais le merle. Tu l'as eu. Chouchou souffle sur la plume. Elle tremble, puis se pose. Elle sent le jardin. Oui. Le cerisier goutte encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à maman. Le jardin sent l'herbe.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cerisier redevient silencieux. Le ver s'est caché sous la feuille. Le merle va revenir ? Peut-être. Tu as eu son cri. Une goutte tombe encore du bois. Elle fait un trou dans la terre noire. Tio tio. C'était le merle. Le chat part vers l'allée. Chouchou reste près du tronc mouillé. Tu voulais le merle. Tu l'as eu. Chouchou souffle sur la plume. Elle tremble, puis se pose. Elle sent le jardin. Oui. Le cerisier goutte encore un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1779,7 +1835,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1851,10 +1907,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amandine donne la main à maman. Le jardin sent l'herbe.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le cerisier redevient silencieux.
+narrateur|Le ver s'est caché sous la feuille.
+enfant-f|Le merle va revenir ?
+maman|Peut-être.
+maman|Tu as eu son cri.
+narrateur|Une goutte tombe encore du bois.
+narrateur|Elle fait un trou dans la terre noire.
+enfant-f|Tio tio.
+maman|C'était le merle.
+narrateur|Le chat part vers l'allée.
+narrateur|Chouchou reste près du tronc mouillé.
+maman|Tu voulais le merle.
+maman|Tu l'as eu.
+narrateur|Chouchou souffle sur la plume.
+narrateur|Elle tremble, puis se pose.
+enfant-f|Elle sent le jardin.
+maman|Oui.
+narrateur|Le cerisier goutte encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une plume du merle reste dans l'herbe. Chouchou tient la main de maman. Il a sifflé. Oui. La terre du jardin reste noire et grasse.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une plume du merle reste dans l'herbe. Chouchou tient la main de maman. Il a sifflé. Oui. La terre du jardin reste noire et grasse.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1940,14 +2012,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2019,10 +2091,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Une plume du merle reste dans l'herbe.
+narrateur|Chouchou tient la main de maman.
+enfant-f|Il a sifflé.
+maman|Oui.
+narrateur|La terre du jardin reste noire et grasse.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin des voisins</t>
+          <t>jardin derrière la maison, terre noire</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amandine, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
